--- a/daily_matches/job_matches_2026-03-09.xlsx
+++ b/daily_matches/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,15 +478,15 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.9</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Copilot, Hugging Face, TensorFlow, PyTorch, Keras, S3, Redshift, BigQuery</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,14 +496,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a9ca0178ffbff15</t>
+          <t>https://www.indeed.com/viewjob?jk=f9a961034c94203e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e4d6385751ba88</t>
+          <t>https://www.indeed.com/viewjob?jk=5360f2e4e078cc82</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,15 +548,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26.7</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Copilot, Hugging Face, TensorFlow, PyTorch, Keras, S3, Redshift, BigQuery, MLflow, Docker</t>
+          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Cassandra, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db40aa076d14f9d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, LLaMA, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Data Lake, FastAPI</t>
+          <t>Data Scientist, AWS SageMaker, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=972ecca486e8cd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,15 +618,15 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, BigQuery, Data Lake, Dataflow, CI/CD, BigQuery</t>
+          <t>Data Scientist, AWS SageMaker, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3902181000a2737</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -653,15 +653,15 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, FastAPI, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,84 +671,84 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c0ff64c20efd0c3</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c200c5f217a8d7</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.8</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, FastAPI, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d374e751f307ea</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,15 +758,15 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, AKS, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a90637d855078256</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,15 +793,15 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, AKS, GitHub Actions, Terraform, Git</t>
+          <t>RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, Kafka, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de027c01e5c0019b</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Generative AI Operations Engineer</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Pinecone, FastAPI, Kubernetes, CI/CD, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8983e071806a0394</t>
+          <t>https://www.indeed.com/viewjob?jk=7f2a4da6c8b29864</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, AKS, GitHub Actions, Terraform, Git</t>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6739cbc12b6628de</t>
+          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,15 +898,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, Jenkins</t>
+          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a0b8313e7245642</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,15 +933,15 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.4</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cb8af80af373eb9</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DataOps/ML Engineer - Remote, Latin America</t>
+          <t>Production Support Executive</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, AWS SageMaker, MLflow, Docker, Kubernetes, CI/CD, Jenkins, Terraform</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086257d35fc77da6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c95915fbd426ea3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps/AI Ops Administrator</t>
+          <t>Software Engineer I - AI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chamberlain Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, FastAPI, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,462 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85f08ece5433f514</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CrowdStrike Charlotte AI Engineer</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, R</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a28833a04fe41c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=17ddf4daef31642b</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>API Enablement Specialist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>VA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Git, Power BI, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e92ce3f72178fa2b</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=30438aff292750ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c15fc57fa4877545</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Java AI / ML Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>S3, Glue, Athena, Redshift, Snowflake, Redshift, Hadoop, Tableau, R, Java</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=306efe4a26e0706c</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>GenAI Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Data Lake, MLflow, Databricks, PySpark, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2ce4778e23223f61</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, PySpark, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=18222a72f279542f</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Pinecone, Prompt Engineering, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf1a71270be8b00</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Senior Artificial Intelligence/Machine Learning Engineer - Remote, Latin America</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Bluelight Consulting</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, LLaMA, TensorFlow, PyTorch, Docker, Kubernetes, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9935e07d8984af95</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, XGBoost, Docker, Kubernetes, CI/CD, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=626fa0a3ab6f27ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Computational Scientist</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Tamarind Bio</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, S3, EC2, Docker, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cc5b4cbfad611e4</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Cloud-Native MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>MA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=130801f04a451d5c</t>
+          <t>https://www.indeed.com/viewjob?jk=447bcc67f82fc3e7</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-09.xlsx
+++ b/daily_matches/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,560 +468,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.8</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9a961034c94203e</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, FAISS, Pinecone, ChromaDB, Prompt Engineering, TensorFlow</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5360f2e4e078cc82</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Senior Software Engineer - Open Data Hub/OpenShift AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Red Hat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MLflow, Docker, Kubernetes, CI/CD, Terraform, Git, Snowflake, Databricks, Cassandra, Tableau</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, MLflow, Kubernetes, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=6bdc41f6b1d7965b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>AI Trainer for Cantonese (Hong Kong)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, AWS SageMaker, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Associate ML Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, AWS SageMaker, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Terraform MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Git, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Docker, Git, Databricks, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MLOps</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, Kafka, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MLOps</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, CI/CD, Snowflake, Databricks, Kafka, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Pinecone, FastAPI, Kubernetes, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f2a4da6c8b29864</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MLOps</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41247af670cd7077</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MLOps</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0e8b67569d1abd</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Kubernetes MLOps Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>NH, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Production Support Executive</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c95915fbd426ea3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Software Engineer I - AI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Chamberlain Group</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Oak Brook, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=447bcc67f82fc3e7</t>
+          <t>https://www.indeed.com/viewjob?jk=eb3b50fded0df74a</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-09.xlsx
+++ b/daily_matches/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, Terraform, Snowflake, Databricks, BigQuery, Python, SQL</t>
+          <t>AI Engineer, Data Scientist, Generative AI, Azure ML, MLflow, CI/CD, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>BITS, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Hadoop, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Open Data Hub/OpenShift AI</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Red Hat</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, MLflow, Kubernetes, Git, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, Kafka, Hadoop, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,357 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bdc41f6b1d7965b</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Trainer for Cantonese (Hong Kong)</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Merrifield, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Docker, CI/CD, Jenkins, Git, Power BI, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Applied Genetics Scientist - Pipeline Data Science</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Syngenta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PyTorch, Keras, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf2eec91a895be79</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Generative AI Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Taxonomist</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer Intern</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cornspring</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb3b50fded0df74a</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c845bfe1dfd51233</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-09.xlsx
+++ b/daily_matches/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Local Lead EB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hallandale Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Azure ML, MLflow, CI/CD, Git, Snowflake, Python, SQL</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=62e0b0ed27a5ec6b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>(1363) Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BITS, Inc.</t>
+          <t>Nearsure</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Hadoop, Python, SQL</t>
+          <t>Generative AI, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
+          <t>https://www.indeed.com/viewjob?jk=f7b52733c5b93b90</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, Kafka, Hadoop, Python, R, Java, Scala</t>
+          <t>Docker, Kubernetes, Terraform, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Swish Analytics Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Merrifield, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Jenkins, Git, Power BI, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, Kubernetes, CI/CD, MySQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,322 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2b18933e9d914c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Applied Genetics Scientist - Pipeline Data Science</t>
+          <t>Sr Data Scientist - Machine Learning</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>PyTorch, Keras, Docker, Kubernetes, Git, NoSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, TensorFlow, BigQuery, Databricks, BigQuery, R, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf2eec91a895be79</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Generative AI Operations Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5233eb09f014a08a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5097254ffda8aa23</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ba1788435dbf136</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=179cc696ce6a3a5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a49578296052b0f</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea6c9de4c26d6a0</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Taxonomist</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Kinesis, Apache Airflow, Kafka, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=68fc2220156f231f</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Data Engineer Intern</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Cornspring</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, PostgreSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c845bfe1dfd51233</t>
+          <t>https://www.indeed.com/viewjob?jk=cefe77ba99b93785</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-09.xlsx
+++ b/daily_matches/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Local Lead EB</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hallandale Beach, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, SQL, R</t>
+          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62e0b0ed27a5ec6b</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>(1363) Senior DevOps Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Nearsure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, AKS, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7b52733c5b93b90</t>
+          <t>https://www.indeed.com/viewjob?jk=cd47f4ab505d2199</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Senior Data Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Stellix</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Foxborough, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Terraform, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>Glue, Redshift, BigQuery, CI/CD, Jenkins, Snowflake, Databricks, BigQuery, Redshift, Hadoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=23da0426139b73c0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Backend Engineer, Real-Time Bidding</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Swish Analytics Inc.</t>
+          <t>Trellis Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Kubernetes, CI/CD, MySQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, RAG, BigQuery, Dataflow, FastAPI, Docker, Kubernetes, BigQuery, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,112 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2b18933e9d914c</t>
+          <t>https://www.indeed.com/viewjob?jk=d834a2b90f81b6fe</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - Machine Learning</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Jenkins, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GenAI Threat Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, BigQuery, Databricks, BigQuery, R, Scala, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cefe77ba99b93785</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior DevOps Software Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IT Industries</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62df2a6d388e5b9f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-09.xlsx
+++ b/daily_matches/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Python</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, Kinesis, Apache Airflow, CI/CD, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,94 +496,94 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=48a3d37ec6e3c854</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Senior AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Transflo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, AKS, GitHub Actions, Terraform, Git</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, TensorFlow</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd47f4ab505d2199</t>
+          <t>https://www.indeed.com/viewjob?jk=317128db35b1c788</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stellix</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Foxborough, MA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Glue, Redshift, BigQuery, CI/CD, Jenkins, Snowflake, Databricks, BigQuery, Redshift, Hadoop</t>
+          <t>Pinecone, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23da0426139b73c0</t>
+          <t>https://www.indeed.com/viewjob?jk=20ebbd1659adab31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer, Real-Time Bidding</t>
+          <t>Senior Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trellis Technologies</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, BigQuery, Dataflow, FastAPI, Docker, Kubernetes, BigQuery, Python, SQL</t>
+          <t>Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d834a2b90f81b6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=de964b64141d192f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Togetherwork</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Jenkins, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>RAG, S3, Glue, Redshift, Data Lake, Kinesis, CI/CD, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,77 +636,357 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Senior MuleSoft Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Green Irony</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
+          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior DevOps Software Engineer</t>
+          <t>Professional Research Assistant</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IT Industries</t>
+          <t>Univeristy Of Colorado Boulder</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, MLflow, Snowflake, BigQuery, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=713c34fce515b47e</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Intern- AI/ML Engineering</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ENERCON SERVICES, INC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Kennesaw, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77c47922f7d85c8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Glue, Athena, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Product Engineer Senior Consultant I (Full Stack Java/AI)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Allstate Insurance</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62df2a6d388e5b9f</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b3ede5765e5e1c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Developer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>EUTECH Chamber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Gemini, Pinecone, Docker, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4aad1013564cc7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Solutions Architect, Cloud &amp; AI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Promevo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3db42a08f08149e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Cloud DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Iselin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38572d6cdf06c0ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer III</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ryder System</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c76b335adc1dbdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Systems Management Analyst, Azure/DevOps - Remote</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18c04073ad856400</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-09.xlsx
+++ b/daily_matches/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AI Developer – Model Creation &amp; Full Stack (Python)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>ECS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, Data Lake, Kinesis, Apache Airflow, CI/CD, Snowflake</t>
+          <t>Data Scientist, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a3d37ec6e3c854</t>
+          <t>https://www.indeed.com/viewjob?jk=3b7ab4a418bdfe39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Transflo</t>
+          <t>The Brite Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, Prompt Engineering, TensorFlow</t>
+          <t>Data Scientist, S3, EC2, Glue, Athena, Redshift, Data Lake, CI/CD, Git, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=317128db35b1c788</t>
+          <t>https://www.indeed.com/viewjob?jk=97fe4fefddbc3bf0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>InformAI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pinecone, Docker, Kubernetes, CI/CD, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>Data Scientist, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ebbd1659adab31</t>
+          <t>https://www.indeed.com/viewjob?jk=86fc1393dcf5eb4a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de964b64141d192f</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e7b74f60e3f76b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Togetherwork</t>
+          <t>Shopmonkey</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, Data Lake, Kinesis, CI/CD, Redshift, Python, SQL</t>
+          <t>Data Scientist, LangChain, Hugging Face, Pinecone, TensorFlow, PyTorch, MLflow, CI/CD, Snowflake, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
+          <t>https://www.indeed.com/viewjob?jk=0802ac126c9a1ff9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Green Irony</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, R, Java</t>
+          <t>Data Scientist, RAG, Cortex, S3, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902ef08f4a0d7d10</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Professional Research Assistant</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Univeristy Of Colorado Boulder</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, MLflow, Snowflake, BigQuery, Python, SQL, R, Java, Optimization</t>
+          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,42 +706,42 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=713c34fce515b47e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd446fe550a8f20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Intern- AI/ML Engineering</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ENERCON SERVICES, INC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Python, R, Optimization</t>
+          <t>TensorFlow, Docker, Kubernetes, CI/CD, Git, Kafka, Hadoop, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c47922f7d85c8e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
@@ -753,20 +753,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Glue, Athena, CI/CD, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Data Lake, Snowflake, Databricks, Kafka, PostgreSQL, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c4bead3a549cf5d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Product Engineer Senior Consultant I (Full Stack Java/AI)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3ede5765e5e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=13cd085f7b3f3343</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EUTECH Chamber</t>
+          <t>Exiger</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Gemini, Pinecone, Docker, Git, Python, R, Java</t>
+          <t>RAG, Prompt Engineering, S3, Snowflake, Kafka, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4aad1013564cc7b</t>
+          <t>https://www.indeed.com/viewjob?jk=b57c7ab0df211106</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solutions Architect, Cloud &amp; AI</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Promevo</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, Jenkins, Git, Tableau, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3db42a08f08149e7</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Terraform, Kafka, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38572d6cdf06c0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI/ML Engineer III</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ryder System</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Git, Databricks, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, FastAPI, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c76b335adc1dbdc</t>
+          <t>https://www.indeed.com/viewjob?jk=969dd367dfbd182d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Systems Management Analyst, Azure/DevOps - Remote</t>
+          <t>Engineer, Machine Learning Engineering (ML Apps)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Terraform, Git, Python, SQL, R, Optimization</t>
+          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,182 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18c04073ad856400</t>
+          <t>https://www.indeed.com/viewjob?jk=ae8d24935da05eb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Zoro</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a589ec468ec221f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LexisNexis Risk Solutions</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, MySQL, MongoDB, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e1586f5989048f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior System Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CMC Productions USA, Inc.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Docker, CI/CD, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1e4918aa5155e586</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tonawanda, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe42b0844bee7c05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a49bfa0d3768c3e2</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-09.xlsx
+++ b/daily_matches/job_matches_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Developer – Model Creation &amp; Full Stack (Python)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ECS</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL</t>
+          <t>S3, Glue, Data Lake, Kinesis, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b7ab4a418bdfe39</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Brite Group</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, Glue, Athena, Redshift, Data Lake, CI/CD, Git, Redshift</t>
+          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks, Kafka, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fe4fefddbc3bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=340a535ec0c84cac</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Software Engineer, Vehicle Pricing, Digital Experience</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>InformAI</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
+          <t>RAG, Docker, Kubernetes, Git, MySQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fc1393dcf5eb4a</t>
+          <t>https://www.indeed.com/viewjob?jk=efe4c24faa73412e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Distinctive Staffing Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
+          <t>TensorFlow, PyTorch, Keras, OpenCV, Azure ML, MLflow, Docker, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e7b74f60e3f76b</t>
+          <t>https://www.indeed.com/viewjob?jk=88f7a8640bb1fab0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior ML Engineer</t>
+          <t>Engineer, Software III</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shopmonkey</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Juan Capistrano, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, Hugging Face, Pinecone, TensorFlow, PyTorch, MLflow, CI/CD, Snowflake, Python</t>
+          <t>RAG, Copilot, Glue, Docker, Kubernetes, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0802ac126c9a1ff9</t>
+          <t>https://www.indeed.com/viewjob?jk=07e035732090d9b3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Cortex, S3, Apache Airflow, CI/CD, GitHub Actions, Terraform, Git, Snowflake</t>
+          <t>RAG, Copilot, Git, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>RAG, Git, Snowflake, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd446fe550a8f20</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Full Stack AI Engineer, Electronic Systems</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TensorFlow, Docker, Kubernetes, CI/CD, Git, Kafka, Hadoop, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, GitHub Actions, Git, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=51c59e7eda65bba2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Development and Product Support (Work Location: In-Office schedule: in Alpharetta, GA)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Global Payments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Data Lake, Snowflake, Databricks, Kafka, PostgreSQL, Power BI, Python, SQL, R</t>
+          <t>TensorFlow, Hadoop, MySQL, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,392 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4bead3a549cf5d</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Falls Church, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=13cd085f7b3f3343</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Junior Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Exiger</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, S3, Snowflake, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b57c7ab0df211106</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Data QA Engineer III</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Preferred Travel Group</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Git, Tableau, Power BI, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>IT Platform Engineer Senior</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>University of Maryland University College</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>College Park, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Power BI, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Falls Church, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, FastAPI, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=969dd367dfbd182d</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Engineer, Machine Learning Engineering (ML Apps)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Generative AI, PyTorch, Docker, CI/CD, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae8d24935da05eb5</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Zoro</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a589ec468ec221f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>LexisNexis Risk Solutions</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Boca Raton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, MySQL, MongoDB, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1586f5989048f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior System Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CMC Productions USA, Inc.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Docker, CI/CD, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e4918aa5155e586</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Linde</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tonawanda, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, Git, Python, SQL, R, Java, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe42b0844bee7c05</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a49bfa0d3768c3e2</t>
+          <t>https://www.indeed.com/viewjob?jk=555b8f191d82d601</t>
         </is>
       </c>
     </row>
